--- a/data/trans_orig/IP33-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP33-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118826</t>
+          <t>118877</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130205</t>
+          <t>129682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130622</t>
+          <t>130695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143106</t>
+          <t>143172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>253947</t>
+          <t>254427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270365</t>
+          <t>271206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27692</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164414</t>
+          <t>164652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177974</t>
+          <t>178332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184820</t>
+          <t>183212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197793</t>
+          <t>197203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351743</t>
+          <t>352271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371964</t>
+          <t>372486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>109361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122284</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123111</t>
+          <t>122478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135245</t>
+          <t>135589</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235771</t>
+          <t>235394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253967</t>
+          <t>254881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14005</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>28260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>32965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>54147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>156591</t>
+          <t>156490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>176699</t>
+          <t>176338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152953</t>
+          <t>150793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172261</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313676</t>
+          <t>313899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343393</t>
+          <t>342467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,82 +3476,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>12985</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>8049</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>19522</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>29010</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>21137</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>37957</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>12985</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>8438</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>29010</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>21119</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>38971</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62719</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>85955</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>116114</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>566588</t>
+          <t>564877</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>596165</t>
+          <t>594431</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>606269</t>
+          <t>604551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>635390</t>
+          <t>635215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1183118</t>
+          <t>1175933</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1224746</t>
+          <t>1220337</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109498</t>
+          <t>109042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123978</t>
+          <t>124348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120195</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136084</t>
+          <t>136688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235252</t>
+          <t>235653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256180</t>
+          <t>257069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158641</t>
+          <t>160096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176945</t>
+          <t>177349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187341</t>
+          <t>187573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203153</t>
+          <t>203453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353064</t>
+          <t>352658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376103</t>
+          <t>377114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>434</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119018</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133366</t>
+          <t>134076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128633</t>
+          <t>128303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143348</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253647</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273785</t>
+          <t>274476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26076</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34844</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45502</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69610</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>149240</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170913</t>
+          <t>169887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149568</t>
+          <t>148988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>168965</t>
+          <t>169531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>306084</t>
+          <t>305504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334366</t>
+          <t>334454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65070</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67080</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58339</t>
+          <t>56958</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>83477</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>132542</t>
+          <t>132476</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>168441</t>
+          <t>172726</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>556665</t>
+          <t>558042</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>591460</t>
+          <t>591356</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>601566</t>
+          <t>603011</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>636165</t>
+          <t>637232</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1170805</t>
+          <t>1170122</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1220342</t>
+          <t>1219588</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28281</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48241</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90861</t>
+          <t>91865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>108225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112584</t>
+          <t>112784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128891</t>
+          <t>128385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209561</t>
+          <t>210068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233137</t>
+          <t>232823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25785</t>
+          <t>24713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19496</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44041</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57779</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82974</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146328</t>
+          <t>146900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164789</t>
+          <t>166014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158283</t>
+          <t>158151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179797</t>
+          <t>179085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311351</t>
+          <t>311909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339697</t>
+          <t>340819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17655</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>21171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47467</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69362</t>
+          <t>69197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109289</t>
+          <t>109292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125691</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106688</t>
+          <t>106260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126281</t>
+          <t>125024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>221147</t>
+          <t>220602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>246074</t>
+          <t>246693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34493</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50767</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44366</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63706</t>
+          <t>64041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89122</t>
+          <t>88383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>131730</t>
+          <t>131266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153472</t>
+          <t>153004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133274</t>
+          <t>133175</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>154728</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270128</t>
+          <t>268591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301835</t>
+          <t>300036</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>51692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>78815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66969</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>105056</t>
+          <t>102944</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>136283</t>
+          <t>137340</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>103168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>137988</t>
+          <t>137808</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>217216</t>
+          <t>217136</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>264103</t>
+          <t>263803</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>495563</t>
+          <t>495523</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>533920</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>532673</t>
+          <t>533092</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>570164</t>
+          <t>572240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1040893</t>
+          <t>1040888</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1096709</t>
+          <t>1095270</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28981</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51162</t>
+          <t>55933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69967</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84601</t>
+          <t>85167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98432</t>
+          <t>98979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73046</t>
+          <t>71862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112308</t>
+          <t>112411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162655</t>
+          <t>162050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207046</t>
+          <t>206071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23947</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16698</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,82 +12695,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>28937</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39546</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>47091</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>37326</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>58780</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>13,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>28937</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>20985</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39080</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>47091</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>35886</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>59015</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147008</t>
+          <t>146752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164652</t>
+          <t>164053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179936</t>
+          <t>179756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205645</t>
+          <t>205309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334247</t>
+          <t>334250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364764</t>
+          <t>364874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>26724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50374</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>80673</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125627</t>
+          <t>126810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158500</t>
+          <t>161207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108471</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135673</t>
+          <t>135884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243801</t>
+          <t>243684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288855</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23939</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>37988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73649</t>
+          <t>71470</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>103859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124131</t>
+          <t>124027</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>124502</t>
+          <t>126548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146383</t>
+          <t>146056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234415</t>
+          <t>235151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264033</t>
+          <t>263626</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47490</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68954</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>106116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>62214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>72798</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107396</t>
+          <t>105621</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>155185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>179924</t>
+          <t>182863</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>244176</t>
+          <t>242084</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>480181</t>
+          <t>482110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>526616</t>
+          <t>529754</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>520163</t>
+          <t>518616</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>577324</t>
+          <t>575470</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1015145</t>
+          <t>1015221</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1093698</t>
+          <t>1091761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
